--- a/Hardware/BOM/BOM.xlsx
+++ b/Hardware/BOM/BOM.xlsx
@@ -1,26 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Downloads\youssefsaeed11004@gmail.com\Power_Supply\Hardware\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A8ACFE-85CC-4BC3-833B-7129F9B9E9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Power Supply BOM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Makers Link</t>
+  </si>
+  <si>
+    <t>PC ATX Power Supply</t>
+  </si>
+  <si>
+    <t>XL4015 DC-DC Step-Down Module</t>
+  </si>
+  <si>
+    <t>DSN-VC288 Dual Display</t>
+  </si>
+  <si>
+    <t>10K Potentiometer</t>
+  </si>
+  <si>
+    <t>Banana Plugs (Red/Black)</t>
+  </si>
+  <si>
+    <t>Rocker Switch</t>
+  </si>
+  <si>
+    <t>Enclosure</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>AC Power Socket 3 Pin Male Plug Connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Power Cable Male</t>
+  </si>
+  <si>
+    <t>Power Resistor 7W 0.1Ω</t>
+  </si>
+  <si>
+    <t>Glass Fuse 3.15A 250V</t>
+  </si>
+  <si>
+    <t>Fuse Holder Wire 250V 10A R3-11</t>
+  </si>
+  <si>
+    <r>
+      <t>Potentiometer Knob (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t xml:space="preserve">6´13´17) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+  </si>
+  <si>
+    <t>Makers Link (Hyperlink)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +131,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Symbol"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,14 +178,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +518,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>900</v>
+      </c>
+      <c r="E2" s="2">
+        <f t="shared" ref="E2:E12" si="0">B2*D2</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>120</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" ref="E9" si="1">B9*D9</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>35</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="2">
+        <f>B13*D13</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="2">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2">
+        <f>B14*D14</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="5">
+        <f>SUM(E2:E14)</f>
+        <v>1450.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:D15"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{7EE0D6F2-56BE-49CE-9DBA-47BFDCA33129}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{74169D71-49EC-4D40-BA7A-607B01C284FE}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{C65DD72A-C7B9-4ACF-BA15-0D97F832ECE5}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{A2C31BB6-C045-45DE-9A27-6F54121B4039}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{A1F2F08F-E1A8-48C8-A4EA-B0313D0B83CB}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{4B920E02-895E-418D-8B3F-6DCAF6CE2F74}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{DD90078F-C2F4-4693-AA57-16D99C410315}"/>
+    <hyperlink ref="C11" r:id="rId8" xr:uid="{FFF400F3-C783-4EBE-BA64-E312972E65D8}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{E3836095-043A-4E3D-9BFF-5A2EFDC53818}"/>
+    <hyperlink ref="C13" r:id="rId10" xr:uid="{24B59830-9BDF-4C5B-A850-072260A349B4}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{EB757169-2D41-4F2D-9E2B-41E5B03E470F}"/>
+    <hyperlink ref="C3" r:id="rId12" xr:uid="{9C442B2A-9E1D-406E-8389-A05DEBF517EE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId13"/>
 </worksheet>
 </file>